--- a/data/trans_orig/CAGE_R-Edad-trans_orig.xlsx
+++ b/data/trans_orig/CAGE_R-Edad-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con consumo de riesgo, consumo perudicial o dependencia al alcohol (CAGE) en 2007</t>
+          <t>Población con consumo de riesgo, consumo perjudicial o dependencia al alcohol (CAGE) en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2031</t>
+          <t>2414</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>13465</t>
+          <t>13277</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>950</t>
+          <t>935</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10199</t>
+          <t>9610</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5171</t>
+          <t>4589</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>17272</t>
+          <t>17632</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,83%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>480599</t>
+          <t>480787</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>492033</t>
+          <t>491650</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>97,31%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,59%</t>
+          <t>99,51%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>457290</t>
+          <t>457879</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>466539</t>
+          <t>466554</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>97,94%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>944281</t>
+          <t>943921</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>956382</t>
+          <t>956964</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,2%</t>
+          <t>98,17%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,46%</t>
+          <t>99,52%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2722</t>
+          <t>2714</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12892</t>
+          <t>13716</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9632</t>
+          <t>8703</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3951</t>
+          <t>3905</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>18147</t>
+          <t>17199</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1166,7 +1166,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,26%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>722597</t>
+          <t>721773</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>732767</t>
+          <t>732775</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,25%</t>
+          <t>98,14%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1224,7 +1224,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>615862</t>
+          <t>616791</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,46%</t>
+          <t>98,61%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1342835</t>
+          <t>1343783</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1357031</t>
+          <t>1357077</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,67%</t>
+          <t>98,74%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1786</t>
+          <t>1767</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10844</t>
+          <t>10463</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5086</t>
+          <t>4851</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2175</t>
+          <t>2766</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>12538</t>
+          <t>12782</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,96%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>627824</t>
+          <t>628205</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>636882</t>
+          <t>636901</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>98,36%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>684658</t>
+          <t>684893</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>99,3%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1315874</t>
+          <t>1315630</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1326237</t>
+          <t>1325646</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>99,04%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,84%</t>
+          <t>99,79%</t>
         </is>
       </c>
     </row>
@@ -1762,97 +1762,97 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>1173</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>2055</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>5893</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>0,23%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>0,4%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>1,14%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="R13" s="2" t="inlineStr">
         <is>
           <t>1173</t>
         </is>
       </c>
-      <c r="L13" s="2" t="inlineStr">
+      <c r="S13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>5884</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,23%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>5872</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>0,11%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>1,14%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>1173</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>6929</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>0,11%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,57%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>517092</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>519147</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>99,6%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,7 +1910,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>509758</t>
+          <t>509749</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1027860</t>
+          <t>1028917</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,33%</t>
+          <t>99,43%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2766</t>
+          <t>2759</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>13596</t>
+          <t>14603</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2145,7 +2145,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6228</t>
+          <t>5178</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3630</t>
+          <t>3550</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>16727</t>
+          <t>15242</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>1,93%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>373114</t>
+          <t>372107</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>383944</t>
+          <t>383951</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,48%</t>
+          <t>96,22%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>99,29%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,7 +2253,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>397758</t>
+          <t>398808</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -2268,7 +2268,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>98,46%</t>
+          <t>98,72%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>773969</t>
+          <t>775454</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>787066</t>
+          <t>787146</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,88%</t>
+          <t>98,07%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,54%</t>
+          <t>99,55%</t>
         </is>
       </c>
     </row>
@@ -2448,97 +2448,97 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>1847</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>0,63%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K19" s="2" t="inlineStr">
+      <c r="R19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>1770</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>0,52%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>1808</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>290736</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>292583</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>341164</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>342934</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>99,48%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>633709</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>635517</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>99,72%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -2796,7 +2796,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>4486</t>
+          <t>5865</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2811,7 +2811,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,62 +2826,62 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>1007</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>2202</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>5065</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>0,19%</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>0,66%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>1007</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>5864</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>0,19%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>0,93%</t>
         </is>
       </c>
     </row>
@@ -2904,7 +2904,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>205397</t>
+          <t>204018</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -2919,7 +2919,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,86%</t>
+          <t>97,21%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>331706</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>333908</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,7 +2974,7 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>537927</t>
+          <t>538726</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>99,07%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>17045</t>
+          <t>17014</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>38902</t>
+          <t>38046</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3154,7 +3154,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>3720</t>
+          <t>4326</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>17659</t>
+          <t>18367</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,47 +3184,47 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
+          <t>0,54%</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>34927</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t>24204</t>
+        </is>
+      </c>
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>47707</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
           <t>0,52%</t>
         </is>
       </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>34927</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="inlineStr">
-        <is>
-          <t>24809</t>
-        </is>
-      </c>
-      <c r="T25" s="2" t="inlineStr">
-        <is>
-          <t>48344</t>
-        </is>
-      </c>
-      <c r="U25" s="2" t="inlineStr">
-        <is>
-          <t>0,52%</t>
-        </is>
-      </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,72%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3237641</t>
+          <t>3238497</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3259498</t>
+          <t>3259529</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,7 +3262,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,84%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3361538</t>
+          <t>3360830</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3375477</t>
+          <t>3374871</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,47 +3297,47 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
+          <t>99,46%</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>99,87%</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>6478</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>6620814</t>
+        </is>
+      </c>
+      <c r="S26" s="2" t="inlineStr">
+        <is>
+          <t>6608034</t>
+        </is>
+      </c>
+      <c r="T26" s="2" t="inlineStr">
+        <is>
+          <t>6631537</t>
+        </is>
+      </c>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
           <t>99,48%</t>
         </is>
       </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t>99,89%</t>
-        </is>
-      </c>
-      <c r="Q26" s="2" t="inlineStr">
-        <is>
-          <t>6478</t>
-        </is>
-      </c>
-      <c r="R26" s="2" t="inlineStr">
-        <is>
-          <t>6620814</t>
-        </is>
-      </c>
-      <c r="S26" s="2" t="inlineStr">
-        <is>
-          <t>6607397</t>
-        </is>
-      </c>
-      <c r="T26" s="2" t="inlineStr">
-        <is>
-          <t>6630932</t>
-        </is>
-      </c>
-      <c r="U26" s="2" t="inlineStr">
-        <is>
-          <t>99,48%</t>
-        </is>
-      </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,28%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,63%</t>
+          <t>99,64%</t>
         </is>
       </c>
     </row>
@@ -3517,7 +3517,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con consumo de riesgo, consumo perudicial o dependencia al alcohol (CAGE) en 2012</t>
+          <t>Población con consumo de riesgo, consumo perjudicial o dependencia al alcohol (CAGE) en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3712,12 +3712,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8169</t>
+          <t>8674</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>22338</t>
+          <t>23143</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3747,12 +3747,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1025</t>
+          <t>1004</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9422</t>
+          <t>9650</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3782,12 +3782,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>11660</t>
+          <t>11544</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>28439</t>
+          <t>27851</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3797,12 +3797,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,15%</t>
         </is>
       </c>
     </row>
@@ -3825,12 +3825,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>431808</t>
+          <t>431003</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>445977</t>
+          <t>445472</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,08%</t>
+          <t>94,9%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,2%</t>
+          <t>98,09%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>420808</t>
+          <t>420580</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>429205</t>
+          <t>429226</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,81%</t>
+          <t>97,76%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,76%</t>
+          <t>99,77%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>855937</t>
+          <t>856525</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>872716</t>
+          <t>872832</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3910,12 +3910,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,78%</t>
+          <t>96,85%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,69%</t>
         </is>
       </c>
     </row>
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8306</t>
+          <t>8166</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>24134</t>
+          <t>23411</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2048</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>8010</t>
+          <t>7978</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>24352</t>
+          <t>22717</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,75%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>662953</t>
+          <t>663676</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>678781</t>
+          <t>678921</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,49%</t>
+          <t>96,59%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>98,81%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>608207</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>610255</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>99,66%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1272990</t>
+          <t>1274625</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1289332</t>
+          <t>1289364</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,12%</t>
+          <t>98,25%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,38%</t>
+          <t>99,39%</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7704</t>
+          <t>7623</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>22191</t>
+          <t>22901</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>2043</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>7297</t>
+          <t>7803</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>21334</t>
+          <t>22252</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,6%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>659672</t>
+          <t>658962</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>674159</t>
+          <t>674240</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,75%</t>
+          <t>96,64%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>98,88%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>708807</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>710850</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>99,71%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1371378</t>
+          <t>1370460</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1385415</t>
+          <t>1384909</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>98,4%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,48%</t>
+          <t>99,44%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5400</t>
+          <t>6141</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>23390</t>
+          <t>23680</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2191</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>6183</t>
+          <t>6347</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>23344</t>
+          <t>24922</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>2,02%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>591227</t>
+          <t>590937</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>609217</t>
+          <t>608476</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,19%</t>
+          <t>96,15%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,12%</t>
+          <t>99,0%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>614008</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>616199</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>99,64%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1207472</t>
+          <t>1205894</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1224633</t>
+          <t>1224469</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,1%</t>
+          <t>97,98%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,5%</t>
+          <t>99,48%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>819</t>
+          <t>822</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>13587</t>
+          <t>13827</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5104,7 +5104,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5124,7 +5124,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4994</t>
+          <t>5048</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5139,7 +5139,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1623</t>
+          <t>1005</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>14159</t>
+          <t>13595</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,55%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>415842</t>
+          <t>415602</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>428610</t>
+          <t>428607</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5212,7 +5212,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,84%</t>
+          <t>96,78%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -5232,7 +5232,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>442806</t>
+          <t>442752</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -5247,7 +5247,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>98,88%</t>
+          <t>98,87%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>863070</t>
+          <t>863634</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>875606</t>
+          <t>876224</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,45%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,82%</t>
+          <t>99,89%</t>
         </is>
       </c>
     </row>
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1034</t>
+          <t>1017</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>12271</t>
+          <t>12299</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5447,7 +5447,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>1970</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1021</t>
+          <t>1028</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>13825</t>
+          <t>13748</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5517,7 +5517,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,07%</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>297515</t>
+          <t>297487</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>308752</t>
+          <t>308769</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5555,7 +5555,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,04%</t>
+          <t>96,03%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>352026</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>353996</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>99,44%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>649957</t>
+          <t>650034</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>662761</t>
+          <t>662754</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5625,7 +5625,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>97,93%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -5775,7 +5775,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>11143</t>
+          <t>11787</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5790,7 +5790,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5805,62 +5805,62 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>2294</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>2127</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>10089</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>0,36%</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>0,55%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>2294</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>11380</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>0,36%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,58%</t>
         </is>
       </c>
     </row>
@@ -5883,7 +5883,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>238708</t>
+          <t>238064</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -5898,7 +5898,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>95,54%</t>
+          <t>95,28%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>386852</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>388979</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>99,45%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5953,7 +5953,7 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>627450</t>
+          <t>628741</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
@@ -5968,7 +5968,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,22%</t>
+          <t>98,42%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>50279</t>
+          <t>50005</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>85946</t>
+          <t>84334</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1986</t>
+          <t>1989</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>11405</t>
+          <t>11445</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>55135</t>
+          <t>55382</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>91422</t>
+          <t>90084</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6203,7 +6203,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,29%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3340833</t>
+          <t>3342445</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3376500</t>
+          <t>3376774</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>97,49%</t>
+          <t>97,54%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,54%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3546904</t>
+          <t>3546864</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3556323</t>
+          <t>3556320</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6893666</t>
+          <t>6895004</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6929953</t>
+          <t>6929706</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6311,7 +6311,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>98,71%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -6496,7 +6496,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con consumo de riesgo, consumo perudicial o dependencia al alcohol (CAGE) en 2016</t>
+          <t>Población con consumo de riesgo, consumo perjudicial o dependencia al alcohol (CAGE) en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6691,12 +6691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2282</t>
+          <t>1949</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>13691</t>
+          <t>12600</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6726,12 +6726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>939</t>
+          <t>934</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8062</t>
+          <t>8152</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6746,7 +6746,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6761,12 +6761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4133</t>
+          <t>3411</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>17207</t>
+          <t>15678</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>1,92%</t>
         </is>
       </c>
     </row>
@@ -6804,12 +6804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>405772</t>
+          <t>406863</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>417181</t>
+          <t>417514</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6819,12 +6819,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,74%</t>
+          <t>97,0%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,46%</t>
+          <t>99,54%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6839,12 +6839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>387693</t>
+          <t>387603</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>394816</t>
+          <t>394821</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6854,7 +6854,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,96%</t>
+          <t>97,94%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -6874,12 +6874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>798011</t>
+          <t>799540</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>811085</t>
+          <t>811807</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>98,08%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,49%</t>
+          <t>99,58%</t>
         </is>
       </c>
     </row>
@@ -7034,12 +7034,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7550</t>
+          <t>8134</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>24319</t>
+          <t>23675</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7049,12 +7049,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7069,12 +7069,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1838</t>
+          <t>1842</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10635</t>
+          <t>9777</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7089,7 +7089,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7104,12 +7104,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>11864</t>
+          <t>12055</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>29748</t>
+          <t>29734</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7119,7 +7119,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -7147,12 +7147,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>566177</t>
+          <t>566821</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>582946</t>
+          <t>582362</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7162,12 +7162,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,88%</t>
+          <t>95,99%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>98,62%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7182,12 +7182,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>552909</t>
+          <t>553767</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>561706</t>
+          <t>561702</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7197,7 +7197,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>98,27%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -7217,12 +7217,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1124292</t>
+          <t>1124306</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1142176</t>
+          <t>1141985</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7237,7 +7237,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,97%</t>
+          <t>98,96%</t>
         </is>
       </c>
     </row>
@@ -7377,12 +7377,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3721</t>
+          <t>3626</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>15659</t>
+          <t>15796</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7392,12 +7392,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7417,7 +7417,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6105</t>
+          <t>6091</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4753</t>
+          <t>4679</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>17725</t>
+          <t>17964</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7462,12 +7462,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,35%</t>
         </is>
       </c>
     </row>
@@ -7490,12 +7490,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>653438</t>
+          <t>653301</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>665376</t>
+          <t>665471</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7505,12 +7505,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>97,64%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,44%</t>
+          <t>99,46%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7525,7 +7525,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>655281</t>
+          <t>655295</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1312758</t>
+          <t>1312519</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1325730</t>
+          <t>1325804</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7575,12 +7575,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,67%</t>
+          <t>98,65%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,64%</t>
+          <t>99,65%</t>
         </is>
       </c>
     </row>
@@ -7720,12 +7720,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4454</t>
+          <t>4492</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>19667</t>
+          <t>20420</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7735,12 +7735,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7755,12 +7755,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1095</t>
+          <t>1101</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8940</t>
+          <t>9222</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7775,7 +7775,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7790,12 +7790,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>6929</t>
+          <t>7715</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>24015</t>
+          <t>23453</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7805,12 +7805,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,81%</t>
         </is>
       </c>
     </row>
@@ -7833,12 +7833,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>626381</t>
+          <t>625628</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>641594</t>
+          <t>641556</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,96%</t>
+          <t>96,84%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,3%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7868,12 +7868,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>640137</t>
+          <t>639855</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>647982</t>
+          <t>647976</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7883,7 +7883,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,62%</t>
+          <t>98,58%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -7903,12 +7903,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1271110</t>
+          <t>1271672</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1288196</t>
+          <t>1287410</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7918,12 +7918,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,15%</t>
+          <t>98,19%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,47%</t>
+          <t>99,4%</t>
         </is>
       </c>
     </row>
@@ -8063,12 +8063,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3375</t>
+          <t>3386</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>16749</t>
+          <t>17169</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8083,7 +8083,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8103,7 +8103,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>10249</t>
+          <t>10610</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8118,7 +8118,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5259</t>
+          <t>5618</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>22766</t>
+          <t>21025</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8148,12 +8148,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,16%</t>
         </is>
       </c>
     </row>
@@ -8176,12 +8176,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>461169</t>
+          <t>460749</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>474543</t>
+          <t>474532</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8191,7 +8191,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,5%</t>
+          <t>96,41%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -8211,7 +8211,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>486600</t>
+          <t>486239</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -8226,7 +8226,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,94%</t>
+          <t>97,86%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -8246,12 +8246,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>952001</t>
+          <t>953742</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>969508</t>
+          <t>969149</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8261,12 +8261,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>97,84%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,46%</t>
+          <t>99,42%</t>
         </is>
       </c>
     </row>
@@ -8411,7 +8411,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5259</t>
+          <t>5456</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8426,7 +8426,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8446,7 +8446,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>6387</t>
+          <t>5430</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8461,7 +8461,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8481,7 +8481,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>6217</t>
+          <t>6912</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8496,7 +8496,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,97%</t>
         </is>
       </c>
     </row>
@@ -8519,7 +8519,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>329071</t>
+          <t>328874</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -8534,7 +8534,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>98,43%</t>
+          <t>98,37%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -8554,7 +8554,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>371375</t>
+          <t>372332</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -8569,7 +8569,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>98,56%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -8589,7 +8589,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>705875</t>
+          <t>705180</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -8604,7 +8604,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>99,03%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -8754,7 +8754,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>4547</t>
+          <t>4592</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8769,7 +8769,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8784,47 +8784,47 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>912</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>2543</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>0,64%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>912</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>4582</t>
+          <t>4572</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8862,7 +8862,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>252451</t>
+          <t>252406</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -8877,7 +8877,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>98,23%</t>
+          <t>98,21%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>397626</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>400169</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8912,12 +8912,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8932,7 +8932,7 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>652585</t>
+          <t>652595</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
@@ -9092,12 +9092,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>36392</t>
+          <t>36011</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>65896</t>
+          <t>65692</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9107,7 +9107,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -9127,12 +9127,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>9745</t>
+          <t>9870</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>28031</t>
+          <t>27129</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9142,12 +9142,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>51351</t>
+          <t>50398</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>85316</t>
+          <t>83590</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,2%</t>
         </is>
       </c>
     </row>
@@ -9205,12 +9205,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3328454</t>
+          <t>3328658</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3357958</t>
+          <t>3358339</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9225,7 +9225,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>98,94%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9240,12 +9240,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3516511</t>
+          <t>3517413</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3534797</t>
+          <t>3534672</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9255,12 +9255,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>99,21%</t>
+          <t>99,23%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>99,73%</t>
+          <t>99,72%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9275,12 +9275,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6853576</t>
+          <t>6855302</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6887541</t>
+          <t>6888494</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9290,12 +9290,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,8%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>99,27%</t>
         </is>
       </c>
     </row>
@@ -9475,7 +9475,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con consumo de riesgo, consumo perudicial o dependencia al alcohol (CAGE) en 2023</t>
+          <t>Población con consumo de riesgo, consumo perjudicial o dependencia al alcohol (CAGE) en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9675,7 +9675,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>869</t>
+          <t>818</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9690,7 +9690,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9705,12 +9705,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>173</t>
+          <t>169</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>13063</t>
+          <t>12080</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -9725,7 +9725,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,18%</t>
+          <t>12,19%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9740,12 +9740,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>474</t>
+          <t>316</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>14151</t>
+          <t>13963</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9755,12 +9755,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,19%</t>
         </is>
       </c>
     </row>
@@ -9783,7 +9783,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>169034</t>
+          <t>169085</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -9798,7 +9798,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>99,49%</t>
+          <t>99,52%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -9818,12 +9818,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>86019</t>
+          <t>87002</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>98909</t>
+          <t>98913</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9833,7 +9833,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>86,82%</t>
+          <t>87,81%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -9853,12 +9853,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>254834</t>
+          <t>255022</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>268511</t>
+          <t>268669</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9868,12 +9868,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,74%</t>
+          <t>94,81%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,82%</t>
+          <t>99,88%</t>
         </is>
       </c>
     </row>
@@ -10013,12 +10013,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2595</t>
+          <t>2333</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>18329</t>
+          <t>18490</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -10028,12 +10028,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10053,7 +10053,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4476</t>
+          <t>4272</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -10068,7 +10068,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10083,12 +10083,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3079</t>
+          <t>2787</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>17188</t>
+          <t>19600</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -10098,12 +10098,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>5,29%</t>
         </is>
       </c>
     </row>
@@ -10126,12 +10126,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>211806</t>
+          <t>211645</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>227540</t>
+          <t>227802</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -10141,12 +10141,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,04%</t>
+          <t>91,97%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>98,99%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10161,7 +10161,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>136236</t>
+          <t>136440</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -10176,7 +10176,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>96,96%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -10196,12 +10196,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>353659</t>
+          <t>351247</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>367768</t>
+          <t>368060</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -10211,12 +10211,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,37%</t>
+          <t>94,71%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>99,25%</t>
         </is>
       </c>
     </row>
@@ -10356,12 +10356,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1190</t>
+          <t>1180</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8928</t>
+          <t>10528</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10376,7 +10376,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>438</t>
+          <t>440</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5599</t>
+          <t>5527</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10411,7 +10411,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10426,12 +10426,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2638</t>
+          <t>2481</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>12562</t>
+          <t>11293</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10441,12 +10441,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,62%</t>
         </is>
       </c>
     </row>
@@ -10469,12 +10469,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>272230</t>
+          <t>270630</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>279968</t>
+          <t>279978</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -10484,7 +10484,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>96,26%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -10504,12 +10504,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>144491</t>
+          <t>144563</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>149652</t>
+          <t>149650</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -10519,7 +10519,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,27%</t>
+          <t>96,32%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -10539,12 +10539,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>418686</t>
+          <t>419955</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>428610</t>
+          <t>428767</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10554,12 +10554,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,09%</t>
+          <t>97,38%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>99,42%</t>
         </is>
       </c>
     </row>
@@ -10699,12 +10699,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2249</t>
+          <t>2337</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12353</t>
+          <t>12916</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10714,12 +10714,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10734,12 +10734,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>660</t>
+          <t>672</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5585</t>
+          <t>6262</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10749,12 +10749,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10769,12 +10769,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4259</t>
+          <t>3964</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>15395</t>
+          <t>15058</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10784,12 +10784,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,85%</t>
         </is>
       </c>
     </row>
@@ -10812,12 +10812,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>327807</t>
+          <t>327244</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>337911</t>
+          <t>337823</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10827,12 +10827,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,37%</t>
+          <t>96,2%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>99,31%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10847,12 +10847,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>181934</t>
+          <t>181257</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>186859</t>
+          <t>186847</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10862,12 +10862,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,02%</t>
+          <t>96,66%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,65%</t>
+          <t>99,64%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10882,12 +10882,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>512284</t>
+          <t>512621</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>523420</t>
+          <t>523715</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10897,12 +10897,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,08%</t>
+          <t>97,15%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,19%</t>
+          <t>99,25%</t>
         </is>
       </c>
     </row>
@@ -11042,12 +11042,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>6498</t>
+          <t>7080</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>19537</t>
+          <t>19500</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -11057,12 +11057,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11077,12 +11077,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1260</t>
+          <t>1521</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>7261</t>
+          <t>7582</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11112,12 +11112,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>9560</t>
+          <t>9554</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>22919</t>
+          <t>22421</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -11132,7 +11132,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,64%</t>
         </is>
       </c>
     </row>
@@ -11155,12 +11155,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>243315</t>
+          <t>243352</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>256354</t>
+          <t>255772</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -11170,12 +11170,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,57%</t>
+          <t>92,58%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,53%</t>
+          <t>97,31%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11190,12 +11190,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>127496</t>
+          <t>127175</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>133497</t>
+          <t>133236</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -11205,12 +11205,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>94,61%</t>
+          <t>94,37%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>98,87%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11225,12 +11225,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>374689</t>
+          <t>375187</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>388048</t>
+          <t>388054</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -11240,7 +11240,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,24%</t>
+          <t>94,36%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -11385,12 +11385,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1700</t>
+          <t>1813</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8449</t>
+          <t>8207</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -11400,12 +11400,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11425,7 +11425,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3457</t>
+          <t>3546</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -11440,7 +11440,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11455,12 +11455,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>738</t>
+          <t>730</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>11268</t>
+          <t>11119</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -11475,7 +11475,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,38%</t>
         </is>
       </c>
     </row>
@@ -11498,12 +11498,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>180846</t>
+          <t>181088</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>187595</t>
+          <t>187482</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11513,12 +11513,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>95,54%</t>
+          <t>95,66%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>99,04%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11533,7 +11533,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>275349</t>
+          <t>275260</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -11548,7 +11548,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>98,73%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -11568,12 +11568,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>456832</t>
+          <t>456981</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>467362</t>
+          <t>467370</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11583,7 +11583,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>97,59%</t>
+          <t>97,62%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -11728,12 +11728,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>572</t>
+          <t>694</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>6196</t>
+          <t>6317</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11743,12 +11743,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11768,7 +11768,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2176</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11783,7 +11783,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11798,12 +11798,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>964</t>
+          <t>971</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>6186</t>
+          <t>5973</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11813,12 +11813,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,72%</t>
         </is>
       </c>
     </row>
@@ -11841,12 +11841,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>93839</t>
+          <t>93718</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>99463</t>
+          <t>99341</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -11856,12 +11856,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>93,81%</t>
+          <t>93,68%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>99,31%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11876,7 +11876,7 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>24420</t>
+          <t>24575</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
@@ -11891,7 +11891,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>91,82%</t>
+          <t>92,4%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -11911,12 +11911,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>120445</t>
+          <t>120658</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>125667</t>
+          <t>125660</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -11926,12 +11926,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>95,11%</t>
+          <t>95,28%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>99,23%</t>
         </is>
       </c>
     </row>
@@ -12071,12 +12071,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>24755</t>
+          <t>25905</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>48734</t>
+          <t>50138</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -12086,12 +12086,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12106,12 +12106,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>5789</t>
+          <t>5657</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>22683</t>
+          <t>24072</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -12121,12 +12121,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12141,12 +12141,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>34586</t>
+          <t>32694</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>64109</t>
+          <t>64580</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -12156,12 +12156,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,49%</t>
         </is>
       </c>
     </row>
@@ -12184,12 +12184,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1524803</t>
+          <t>1523399</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1548782</t>
+          <t>1547632</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -12199,12 +12199,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>96,81%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,43%</t>
+          <t>98,35%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12219,12 +12219,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>994878</t>
+          <t>993489</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1011772</t>
+          <t>1011904</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -12234,12 +12234,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>97,63%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>99,44%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12254,12 +12254,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2526989</t>
+          <t>2526518</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>2556512</t>
+          <t>2558404</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12269,12 +12269,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>97,53%</t>
+          <t>97,51%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>98,67%</t>
+          <t>98,74%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/CAGE_R-Edad-trans_orig.xlsx
+++ b/data/trans_orig/CAGE_R-Edad-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2414</t>
+          <t>2661</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>13277</t>
+          <t>13846</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>935</t>
+          <t>949</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9610</t>
+          <t>9568</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4589</t>
+          <t>4553</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>17632</t>
+          <t>17234</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,79%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>480787</t>
+          <t>480218</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>491650</t>
+          <t>491403</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,31%</t>
+          <t>97,2%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,51%</t>
+          <t>99,46%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>457879</t>
+          <t>457921</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>466554</t>
+          <t>466540</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,94%</t>
+          <t>97,95%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>943921</t>
+          <t>944319</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>956964</t>
+          <t>957000</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,17%</t>
+          <t>98,21%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,52%</t>
+          <t>99,53%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2714</t>
+          <t>2531</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13716</t>
+          <t>13619</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8703</t>
+          <t>9702</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3905</t>
+          <t>4323</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>17199</t>
+          <t>18166</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,33%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>721773</t>
+          <t>721870</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>732775</t>
+          <t>732958</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,14%</t>
+          <t>98,15%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,63%</t>
+          <t>99,66%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,7 +1224,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>616791</t>
+          <t>615792</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,61%</t>
+          <t>98,45%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1343783</t>
+          <t>1342816</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1357077</t>
+          <t>1356659</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,67%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,71%</t>
+          <t>99,68%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1767</t>
+          <t>1925</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10463</t>
+          <t>11565</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4851</t>
+          <t>5085</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2766</t>
+          <t>2726</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>12782</t>
+          <t>12755</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>628205</t>
+          <t>627103</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>636901</t>
+          <t>636743</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,36%</t>
+          <t>98,19%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,72%</t>
+          <t>99,7%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>684893</t>
+          <t>684659</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>99,26%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1315630</t>
+          <t>1315657</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1325646</t>
+          <t>1325686</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1802,7 +1802,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5893</t>
+          <t>6690</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1817,7 +1817,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1837,7 +1837,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>5872</t>
+          <t>5869</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1910,7 +1910,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>509749</t>
+          <t>508952</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -1925,7 +1925,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,86%</t>
+          <t>98,7%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1028917</t>
+          <t>1028920</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2759</t>
+          <t>2846</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>14603</t>
+          <t>14429</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2145,7 +2145,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5178</t>
+          <t>5458</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3550</t>
+          <t>3744</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>15242</t>
+          <t>16387</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>2,07%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>372107</t>
+          <t>372281</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>383951</t>
+          <t>383864</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,22%</t>
+          <t>96,27%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,29%</t>
+          <t>99,26%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,7 +2253,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>398808</t>
+          <t>398528</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -2268,7 +2268,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>98,65%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>775454</t>
+          <t>774309</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>787146</t>
+          <t>786952</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,07%</t>
+          <t>97,93%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,55%</t>
+          <t>99,53%</t>
         </is>
       </c>
     </row>
@@ -2796,7 +2796,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>5865</t>
+          <t>5084</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2811,7 +2811,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>5065</t>
+          <t>5067</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2904,7 +2904,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>204018</t>
+          <t>204799</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -2919,7 +2919,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,21%</t>
+          <t>97,58%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2974,7 +2974,7 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>538726</t>
+          <t>538724</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>17014</t>
+          <t>16852</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>38046</t>
+          <t>37973</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,82 +3149,82 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
+          <t>0,51%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>1,16%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>9289</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>4632</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>18511</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>0,27%</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>0,14%</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>0,55%</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>34927</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t>24974</t>
+        </is>
+      </c>
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>48973</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
           <t>0,52%</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>1,16%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>9289</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>4326</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>18367</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>0,27%</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t>0,13%</t>
-        </is>
-      </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>0,54%</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>34927</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="inlineStr">
-        <is>
-          <t>24204</t>
-        </is>
-      </c>
-      <c r="T25" s="2" t="inlineStr">
-        <is>
-          <t>47707</t>
-        </is>
-      </c>
-      <c r="U25" s="2" t="inlineStr">
-        <is>
-          <t>0,52%</t>
-        </is>
-      </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,74%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3238497</t>
+          <t>3238570</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3259529</t>
+          <t>3259691</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3267,77 +3267,77 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
+          <t>99,49%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>3289</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>3369908</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>3360686</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>3374565</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>99,73%</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>99,45%</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>99,86%</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>6478</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>6620814</t>
+        </is>
+      </c>
+      <c r="S26" s="2" t="inlineStr">
+        <is>
+          <t>6606768</t>
+        </is>
+      </c>
+      <c r="T26" s="2" t="inlineStr">
+        <is>
+          <t>6630767</t>
+        </is>
+      </c>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
           <t>99,48%</t>
         </is>
       </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>3289</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>3369908</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>3360830</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>3374871</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>99,73%</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>99,46%</t>
-        </is>
-      </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t>99,87%</t>
-        </is>
-      </c>
-      <c r="Q26" s="2" t="inlineStr">
-        <is>
-          <t>6478</t>
-        </is>
-      </c>
-      <c r="R26" s="2" t="inlineStr">
-        <is>
-          <t>6620814</t>
-        </is>
-      </c>
-      <c r="S26" s="2" t="inlineStr">
-        <is>
-          <t>6608034</t>
-        </is>
-      </c>
-      <c r="T26" s="2" t="inlineStr">
-        <is>
-          <t>6631537</t>
-        </is>
-      </c>
-      <c r="U26" s="2" t="inlineStr">
-        <is>
-          <t>99,48%</t>
-        </is>
-      </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>99,26%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,64%</t>
+          <t>99,62%</t>
         </is>
       </c>
     </row>
@@ -3712,12 +3712,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8674</t>
+          <t>8089</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>23143</t>
+          <t>23122</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3747,12 +3747,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1004</t>
+          <t>1013</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9650</t>
+          <t>10520</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3782,12 +3782,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>11544</t>
+          <t>11098</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>27851</t>
+          <t>27602</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3797,12 +3797,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,12%</t>
         </is>
       </c>
     </row>
@@ -3825,12 +3825,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>431003</t>
+          <t>431024</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>445472</t>
+          <t>446057</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,9%</t>
+          <t>94,91%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>98,22%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>420580</t>
+          <t>419710</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>429226</t>
+          <t>429217</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,76%</t>
+          <t>97,55%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,77%</t>
+          <t>99,76%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>856525</t>
+          <t>856774</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>872832</t>
+          <t>873278</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3910,12 +3910,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,85%</t>
+          <t>96,88%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>98,75%</t>
         </is>
       </c>
     </row>
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8166</t>
+          <t>8249</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>23411</t>
+          <t>23148</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>7978</t>
+          <t>8765</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>22717</t>
+          <t>24751</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,91%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>663676</t>
+          <t>663939</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>678921</t>
+          <t>678838</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,59%</t>
+          <t>96,63%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,8%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1274625</t>
+          <t>1272591</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1289364</t>
+          <t>1288577</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,25%</t>
+          <t>98,09%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>99,32%</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7623</t>
+          <t>7479</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>22901</t>
+          <t>22145</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>7803</t>
+          <t>7276</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>22252</t>
+          <t>22351</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4483,7 +4483,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>658962</t>
+          <t>659718</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>674240</t>
+          <t>674384</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,64%</t>
+          <t>96,75%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,88%</t>
+          <t>98,9%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1370460</t>
+          <t>1370361</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1384909</t>
+          <t>1385436</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4601,7 +4601,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,44%</t>
+          <t>99,48%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6141</t>
+          <t>6203</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>23680</t>
+          <t>24583</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>6347</t>
+          <t>5966</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>24922</t>
+          <t>23530</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,91%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>590937</t>
+          <t>590034</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>608476</t>
+          <t>608414</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,15%</t>
+          <t>96,0%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,0%</t>
+          <t>98,99%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1205894</t>
+          <t>1207286</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1224469</t>
+          <t>1224850</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,98%</t>
+          <t>98,09%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,48%</t>
+          <t>99,52%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>822</t>
+          <t>815</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>13827</t>
+          <t>13223</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5104,7 +5104,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5124,7 +5124,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5048</t>
+          <t>5005</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5139,7 +5139,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1005</t>
+          <t>1781</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>13595</t>
+          <t>13862</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,58%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>415602</t>
+          <t>416206</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>428607</t>
+          <t>428614</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5212,7 +5212,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,78%</t>
+          <t>96,92%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -5232,7 +5232,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>442752</t>
+          <t>442795</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -5247,7 +5247,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>98,88%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>863634</t>
+          <t>863367</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>876224</t>
+          <t>875448</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,45%</t>
+          <t>98,42%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,89%</t>
+          <t>99,8%</t>
         </is>
       </c>
     </row>
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1017</t>
+          <t>1871</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>12299</t>
+          <t>13100</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1028</t>
+          <t>1877</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>13748</t>
+          <t>13002</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>1,96%</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>297487</t>
+          <t>296686</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>308769</t>
+          <t>307915</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,03%</t>
+          <t>95,77%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,67%</t>
+          <t>99,4%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>650034</t>
+          <t>650780</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>662754</t>
+          <t>661905</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>97,93%</t>
+          <t>98,04%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,85%</t>
+          <t>99,72%</t>
         </is>
       </c>
     </row>
@@ -5775,7 +5775,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>11787</t>
+          <t>11114</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5790,7 +5790,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5845,7 +5845,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>10089</t>
+          <t>11376</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5860,7 +5860,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,78%</t>
         </is>
       </c>
     </row>
@@ -5883,7 +5883,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>238064</t>
+          <t>238737</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -5898,7 +5898,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>95,28%</t>
+          <t>95,55%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -5953,7 +5953,7 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>628741</t>
+          <t>627454</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
@@ -5968,7 +5968,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,42%</t>
+          <t>98,22%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>50005</t>
+          <t>49698</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>84334</t>
+          <t>84873</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1989</t>
+          <t>1979</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>11445</t>
+          <t>12225</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6168,7 +6168,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>55382</t>
+          <t>55520</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>90084</t>
+          <t>90574</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6203,7 +6203,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,3%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3342445</t>
+          <t>3341906</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3376774</t>
+          <t>3377081</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>97,54%</t>
+          <t>97,52%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,55%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3546864</t>
+          <t>3546084</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3556320</t>
+          <t>3556330</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6276,7 +6276,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>99,68%</t>
+          <t>99,66%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6895004</t>
+          <t>6894514</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6929706</t>
+          <t>6929568</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6311,7 +6311,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,7%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -6691,12 +6691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1949</t>
+          <t>2065</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>12600</t>
+          <t>13490</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6726,12 +6726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>934</t>
+          <t>938</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8152</t>
+          <t>8149</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6761,12 +6761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3411</t>
+          <t>3962</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>15678</t>
+          <t>16987</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>2,08%</t>
         </is>
       </c>
     </row>
@@ -6804,12 +6804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>406863</t>
+          <t>405973</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>417514</t>
+          <t>417398</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6819,12 +6819,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,0%</t>
+          <t>96,78%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,54%</t>
+          <t>99,51%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6839,12 +6839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>387603</t>
+          <t>387606</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>394821</t>
+          <t>394817</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6874,12 +6874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>799540</t>
+          <t>798231</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>811807</t>
+          <t>811256</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>97,92%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,58%</t>
+          <t>99,51%</t>
         </is>
       </c>
     </row>
@@ -7034,12 +7034,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8134</t>
+          <t>8295</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>23675</t>
+          <t>24147</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7049,12 +7049,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7069,12 +7069,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1842</t>
+          <t>1856</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9777</t>
+          <t>10591</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7089,7 +7089,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7104,12 +7104,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>12055</t>
+          <t>12045</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>29734</t>
+          <t>30637</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7124,7 +7124,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,65%</t>
         </is>
       </c>
     </row>
@@ -7147,12 +7147,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>566821</t>
+          <t>566349</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>582362</t>
+          <t>582201</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7162,12 +7162,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,99%</t>
+          <t>95,91%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,62%</t>
+          <t>98,6%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7182,12 +7182,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>553767</t>
+          <t>552953</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>561702</t>
+          <t>561688</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7197,7 +7197,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,27%</t>
+          <t>98,12%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -7217,12 +7217,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1124306</t>
+          <t>1123403</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1141985</t>
+          <t>1141995</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7232,7 +7232,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,42%</t>
+          <t>97,35%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -7377,12 +7377,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3626</t>
+          <t>3821</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>15796</t>
+          <t>14794</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7392,12 +7392,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7417,7 +7417,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6091</t>
+          <t>5447</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7432,7 +7432,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4679</t>
+          <t>4922</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>17964</t>
+          <t>18237</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7462,12 +7462,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,37%</t>
         </is>
       </c>
     </row>
@@ -7490,12 +7490,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>653301</t>
+          <t>654303</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>665471</t>
+          <t>665276</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7505,12 +7505,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,64%</t>
+          <t>97,79%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,46%</t>
+          <t>99,43%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7525,7 +7525,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>655295</t>
+          <t>655939</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -7540,7 +7540,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>99,18%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1312519</t>
+          <t>1312246</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1325804</t>
+          <t>1325561</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7575,12 +7575,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,63%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,65%</t>
+          <t>99,63%</t>
         </is>
       </c>
     </row>
@@ -7720,12 +7720,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4492</t>
+          <t>4884</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>20420</t>
+          <t>18823</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7735,12 +7735,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7760,7 +7760,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>9222</t>
+          <t>9923</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7775,7 +7775,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7790,12 +7790,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>7715</t>
+          <t>7312</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>23453</t>
+          <t>25324</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7805,12 +7805,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,96%</t>
         </is>
       </c>
     </row>
@@ -7833,12 +7833,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>625628</t>
+          <t>627225</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>641556</t>
+          <t>641164</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,84%</t>
+          <t>97,09%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>99,24%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7868,7 +7868,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>639855</t>
+          <t>639154</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -7883,7 +7883,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,47%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -7903,12 +7903,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1271672</t>
+          <t>1269801</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1287410</t>
+          <t>1287813</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7918,12 +7918,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,19%</t>
+          <t>98,04%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,4%</t>
+          <t>99,44%</t>
         </is>
       </c>
     </row>
@@ -8063,12 +8063,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3386</t>
+          <t>3422</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>17169</t>
+          <t>17390</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8078,12 +8078,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8103,7 +8103,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>10610</t>
+          <t>10709</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8118,7 +8118,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5618</t>
+          <t>5203</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>21025</t>
+          <t>20203</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8148,12 +8148,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,07%</t>
         </is>
       </c>
     </row>
@@ -8176,12 +8176,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>460749</t>
+          <t>460528</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>474532</t>
+          <t>474496</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8191,12 +8191,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,41%</t>
+          <t>96,36%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,29%</t>
+          <t>99,28%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8211,7 +8211,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>486239</t>
+          <t>486140</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -8226,7 +8226,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,86%</t>
+          <t>97,84%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -8246,12 +8246,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>953742</t>
+          <t>954564</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>969149</t>
+          <t>969564</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8261,12 +8261,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,84%</t>
+          <t>97,93%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,42%</t>
+          <t>99,47%</t>
         </is>
       </c>
     </row>
@@ -8411,7 +8411,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5456</t>
+          <t>4826</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8426,7 +8426,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8446,7 +8446,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5430</t>
+          <t>5393</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8461,7 +8461,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8481,7 +8481,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>6912</t>
+          <t>7146</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8496,7 +8496,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,0%</t>
         </is>
       </c>
     </row>
@@ -8519,7 +8519,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>328874</t>
+          <t>329504</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -8534,7 +8534,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>98,56%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -8554,7 +8554,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>372332</t>
+          <t>372369</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -8569,7 +8569,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>98,57%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -8589,7 +8589,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>705180</t>
+          <t>704946</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -8604,7 +8604,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>99,0%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -8754,7 +8754,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>4592</t>
+          <t>4911</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8769,7 +8769,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8824,7 +8824,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>4572</t>
+          <t>5287</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8839,7 +8839,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,8%</t>
         </is>
       </c>
     </row>
@@ -8862,7 +8862,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>252406</t>
+          <t>252087</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -8877,7 +8877,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>98,09%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -8932,7 +8932,7 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>652595</t>
+          <t>651880</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
@@ -8947,7 +8947,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>99,2%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -9092,12 +9092,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>36011</t>
+          <t>36001</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>65692</t>
+          <t>64060</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9112,7 +9112,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9127,12 +9127,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>9870</t>
+          <t>9260</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>27129</t>
+          <t>26200</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9142,12 +9142,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>50398</t>
+          <t>51207</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>83590</t>
+          <t>83935</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,21%</t>
         </is>
       </c>
     </row>
@@ -9205,12 +9205,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3328658</t>
+          <t>3330290</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3358339</t>
+          <t>3358349</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9220,7 +9220,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>98,06%</t>
+          <t>98,11%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -9240,12 +9240,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3517413</t>
+          <t>3518342</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3534672</t>
+          <t>3535282</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9255,12 +9255,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,26%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>99,72%</t>
+          <t>99,74%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9275,12 +9275,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6855302</t>
+          <t>6854957</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6888494</t>
+          <t>6887685</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9290,12 +9290,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,79%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,26%</t>
         </is>
       </c>
     </row>
@@ -9665,7 +9665,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>165</t>
+          <t>1653</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -9675,12 +9675,12 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>818</t>
+          <t>8771</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -9690,7 +9690,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9700,32 +9700,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>4001</t>
+          <t>6178</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>169</t>
+          <t>1687</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>12080</t>
+          <t>15358</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>13,84%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9735,32 +9735,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>4166</t>
+          <t>7831</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>316</t>
+          <t>2186</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>13963</t>
+          <t>20157</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>7,27%</t>
         </is>
       </c>
     </row>
@@ -9778,27 +9778,27 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>169738</t>
+          <t>164590</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>169085</t>
+          <t>157472</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>169903</t>
+          <t>166243</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>99,9%</t>
+          <t>99,01%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>99,52%</t>
+          <t>94,72%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -9813,32 +9813,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>95081</t>
+          <t>104817</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>87002</t>
+          <t>95637</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>98913</t>
+          <t>109308</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>95,96%</t>
+          <t>94,43%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>87,81%</t>
+          <t>86,16%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,83%</t>
+          <t>98,48%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9848,32 +9848,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>264819</t>
+          <t>269407</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>255022</t>
+          <t>257081</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>268669</t>
+          <t>275052</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>98,45%</t>
+          <t>97,18%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,81%</t>
+          <t>92,73%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,88%</t>
+          <t>99,21%</t>
         </is>
       </c>
     </row>
@@ -9891,17 +9891,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>169903</t>
+          <t>166243</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>169903</t>
+          <t>166243</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>169903</t>
+          <t>166243</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9926,17 +9926,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>99082</t>
+          <t>110995</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>99082</t>
+          <t>110995</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>99082</t>
+          <t>110995</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9961,17 +9961,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>268985</t>
+          <t>277238</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>268985</t>
+          <t>277238</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>268985</t>
+          <t>277238</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -10008,32 +10008,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7295</t>
+          <t>7996</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2333</t>
+          <t>3000</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>18490</t>
+          <t>18137</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10043,7 +10043,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>857</t>
+          <t>861</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -10053,12 +10053,12 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4272</t>
+          <t>4271</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
@@ -10068,7 +10068,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10078,32 +10078,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>8152</t>
+          <t>8857</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2787</t>
+          <t>3521</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>19600</t>
+          <t>19125</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>4,77%</t>
         </is>
       </c>
     </row>
@@ -10121,32 +10121,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>222840</t>
+          <t>241468</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>211645</t>
+          <t>231327</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>227802</t>
+          <t>246464</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>96,83%</t>
+          <t>96,79%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,97%</t>
+          <t>92,73%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>98,8%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10156,27 +10156,27 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>139855</t>
+          <t>150647</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>136440</t>
+          <t>147237</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>140712</t>
+          <t>151508</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>99,43%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,96%</t>
+          <t>97,18%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -10191,32 +10191,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>362695</t>
+          <t>392115</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>351247</t>
+          <t>381847</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>368060</t>
+          <t>397451</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>97,79%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,71%</t>
+          <t>95,23%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,12%</t>
         </is>
       </c>
     </row>
@@ -10234,17 +10234,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>230135</t>
+          <t>249464</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>230135</t>
+          <t>249464</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>230135</t>
+          <t>249464</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -10269,17 +10269,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>140712</t>
+          <t>151508</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>140712</t>
+          <t>151508</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>140712</t>
+          <t>151508</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10304,17 +10304,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>370847</t>
+          <t>400972</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>370847</t>
+          <t>400972</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>370847</t>
+          <t>400972</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10351,32 +10351,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>3649</t>
+          <t>5727</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1180</t>
+          <t>2242</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10528</t>
+          <t>12606</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10386,32 +10386,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>1952</t>
+          <t>2087</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>440</t>
+          <t>460</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5527</t>
+          <t>5707</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10421,32 +10421,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>5601</t>
+          <t>7815</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2481</t>
+          <t>3557</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>11293</t>
+          <t>15433</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>3,21%</t>
         </is>
       </c>
     </row>
@@ -10464,32 +10464,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>277509</t>
+          <t>305916</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>270630</t>
+          <t>299037</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>279978</t>
+          <t>309401</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,16%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,26%</t>
+          <t>95,96%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,58%</t>
+          <t>99,28%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10499,32 +10499,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>148138</t>
+          <t>167062</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>144563</t>
+          <t>163442</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>149650</t>
+          <t>168689</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,77%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,32%</t>
+          <t>96,63%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,71%</t>
+          <t>99,73%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10534,32 +10534,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>425647</t>
+          <t>472976</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>419955</t>
+          <t>465358</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>428767</t>
+          <t>477234</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,37%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,38%</t>
+          <t>96,79%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,42%</t>
+          <t>99,26%</t>
         </is>
       </c>
     </row>
@@ -10577,17 +10577,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>281158</t>
+          <t>311643</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>281158</t>
+          <t>311643</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>281158</t>
+          <t>311643</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10612,17 +10612,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>150090</t>
+          <t>169149</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>150090</t>
+          <t>169149</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>150090</t>
+          <t>169149</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10647,17 +10647,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>431248</t>
+          <t>480791</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>431248</t>
+          <t>480791</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>431248</t>
+          <t>480791</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10694,32 +10694,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>6101</t>
+          <t>6910</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2337</t>
+          <t>2943</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12916</t>
+          <t>13461</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10729,32 +10729,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2151</t>
+          <t>2819</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>672</t>
+          <t>711</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6262</t>
+          <t>6434</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10764,32 +10764,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>8252</t>
+          <t>9729</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3964</t>
+          <t>5222</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>15058</t>
+          <t>17298</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>3,1%</t>
         </is>
       </c>
     </row>
@@ -10807,32 +10807,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>334059</t>
+          <t>342849</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>327244</t>
+          <t>336298</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>337823</t>
+          <t>346816</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>98,02%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,2%</t>
+          <t>96,15%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,16%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10842,32 +10842,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>185368</t>
+          <t>204879</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>181257</t>
+          <t>201264</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>186847</t>
+          <t>206987</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>98,64%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,66%</t>
+          <t>96,9%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,64%</t>
+          <t>99,66%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10877,32 +10877,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>519427</t>
+          <t>547728</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>512621</t>
+          <t>540159</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>523715</t>
+          <t>552235</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>98,44%</t>
+          <t>98,25%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,15%</t>
+          <t>96,9%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,06%</t>
         </is>
       </c>
     </row>
@@ -10920,17 +10920,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>340160</t>
+          <t>349759</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>340160</t>
+          <t>349759</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>340160</t>
+          <t>349759</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -10955,17 +10955,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>187519</t>
+          <t>207698</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>187519</t>
+          <t>207698</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>187519</t>
+          <t>207698</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -10990,17 +10990,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>527679</t>
+          <t>557457</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>527679</t>
+          <t>557457</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>527679</t>
+          <t>557457</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -11037,32 +11037,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>11716</t>
+          <t>11601</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>7080</t>
+          <t>6709</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>19500</t>
+          <t>18951</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11072,32 +11072,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>3544</t>
+          <t>3813</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1521</t>
+          <t>1661</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>7582</t>
+          <t>7837</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11107,32 +11107,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>15260</t>
+          <t>15414</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>9554</t>
+          <t>9451</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>22421</t>
+          <t>23109</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,41%</t>
         </is>
       </c>
     </row>
@@ -11150,32 +11150,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>251136</t>
+          <t>267760</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>243352</t>
+          <t>260410</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>255772</t>
+          <t>272652</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>95,54%</t>
+          <t>95,85%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,58%</t>
+          <t>93,22%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,31%</t>
+          <t>97,6%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11185,32 +11185,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>131213</t>
+          <t>144145</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>127175</t>
+          <t>140121</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>133236</t>
+          <t>146297</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>97,37%</t>
+          <t>97,42%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>94,37%</t>
+          <t>94,7%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>98,88%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11220,32 +11220,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>382348</t>
+          <t>411904</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>375187</t>
+          <t>404209</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>388054</t>
+          <t>417867</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>96,16%</t>
+          <t>96,39%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,36%</t>
+          <t>94,59%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,6%</t>
+          <t>97,79%</t>
         </is>
       </c>
     </row>
@@ -11263,17 +11263,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>262852</t>
+          <t>279361</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>262852</t>
+          <t>279361</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>262852</t>
+          <t>279361</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11298,17 +11298,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>134757</t>
+          <t>147958</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>134757</t>
+          <t>147958</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>134757</t>
+          <t>147958</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11333,17 +11333,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>397608</t>
+          <t>427318</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>397608</t>
+          <t>427318</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>397608</t>
+          <t>427318</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11380,32 +11380,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>3996</t>
+          <t>4876</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1813</t>
+          <t>1964</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8207</t>
+          <t>9462</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11415,7 +11415,7 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>450</t>
+          <t>457</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
@@ -11425,12 +11425,12 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3546</t>
+          <t>1895</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
@@ -11440,7 +11440,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11450,32 +11450,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>4446</t>
+          <t>5333</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>730</t>
+          <t>2500</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>11119</t>
+          <t>10380</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>3,63%</t>
         </is>
       </c>
     </row>
@@ -11493,32 +11493,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>185299</t>
+          <t>202216</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>181088</t>
+          <t>197630</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>187482</t>
+          <t>205128</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>97,65%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>95,66%</t>
+          <t>95,43%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>99,05%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11528,27 +11528,27 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>278356</t>
+          <t>78441</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>275260</t>
+          <t>77003</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>278806</t>
+          <t>78898</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>99,84%</t>
+          <t>99,42%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>97,6%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -11563,32 +11563,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>463654</t>
+          <t>280657</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>456981</t>
+          <t>275610</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>467370</t>
+          <t>283490</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>98,14%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>96,37%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,84%</t>
+          <t>99,13%</t>
         </is>
       </c>
     </row>
@@ -11606,17 +11606,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>189295</t>
+          <t>207092</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>189295</t>
+          <t>207092</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>189295</t>
+          <t>207092</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11641,17 +11641,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>278806</t>
+          <t>78898</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>278806</t>
+          <t>78898</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>278806</t>
+          <t>78898</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11676,17 +11676,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>468100</t>
+          <t>285990</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>468100</t>
+          <t>285990</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>468100</t>
+          <t>285990</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11723,32 +11723,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>2383</t>
+          <t>2448</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>694</t>
+          <t>568</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>6317</t>
+          <t>5850</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11758,7 +11758,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>404</t>
+          <t>431</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
@@ -11768,12 +11768,12 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2245</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
@@ -11783,7 +11783,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11793,32 +11793,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>2787</t>
+          <t>2879</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>971</t>
+          <t>980</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>5973</t>
+          <t>6711</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,8%</t>
         </is>
       </c>
     </row>
@@ -11836,32 +11836,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>97652</t>
+          <t>107293</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>93718</t>
+          <t>103891</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>99341</t>
+          <t>109173</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>97,77%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>93,68%</t>
+          <t>94,67%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,48%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11871,27 +11871,27 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>26192</t>
+          <t>29689</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>24575</t>
+          <t>27875</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>26596</t>
+          <t>30120</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>98,57%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>92,4%</t>
+          <t>92,55%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -11906,32 +11906,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>123844</t>
+          <t>136982</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>120658</t>
+          <t>133150</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>125660</t>
+          <t>138881</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>97,94%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>95,28%</t>
+          <t>95,2%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,3%</t>
         </is>
       </c>
     </row>
@@ -11949,17 +11949,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>100035</t>
+          <t>109741</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>100035</t>
+          <t>109741</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>100035</t>
+          <t>109741</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11984,17 +11984,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>26596</t>
+          <t>30120</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>26596</t>
+          <t>30120</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>26596</t>
+          <t>30120</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -12019,17 +12019,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>126631</t>
+          <t>139861</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>126631</t>
+          <t>139861</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>126631</t>
+          <t>139861</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -12066,32 +12066,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>35306</t>
+          <t>41211</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>25905</t>
+          <t>29825</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>50138</t>
+          <t>55525</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12101,32 +12101,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>13359</t>
+          <t>16647</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>5657</t>
+          <t>9748</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>24072</t>
+          <t>28483</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12136,32 +12136,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>48664</t>
+          <t>57858</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>32694</t>
+          <t>44071</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>64580</t>
+          <t>74386</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,89%</t>
         </is>
       </c>
     </row>
@@ -12179,32 +12179,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>1538231</t>
+          <t>1632092</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1523399</t>
+          <t>1617778</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1547632</t>
+          <t>1643478</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>97,76%</t>
+          <t>97,54%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>96,81%</t>
+          <t>96,68%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>98,22%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12214,32 +12214,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>1004202</t>
+          <t>879679</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>993489</t>
+          <t>867843</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1011904</t>
+          <t>886578</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>98,14%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>97,63%</t>
+          <t>96,82%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>99,44%</t>
+          <t>98,91%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12249,32 +12249,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>2542434</t>
+          <t>2511770</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2526518</t>
+          <t>2495242</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>2558404</t>
+          <t>2525557</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>98,12%</t>
+          <t>97,75%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>97,51%</t>
+          <t>97,11%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,28%</t>
         </is>
       </c>
     </row>
@@ -12292,17 +12292,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>1573537</t>
+          <t>1673303</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1573537</t>
+          <t>1673303</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>1573537</t>
+          <t>1673303</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -12327,17 +12327,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>1017561</t>
+          <t>896326</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1017561</t>
+          <t>896326</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>1017561</t>
+          <t>896326</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -12362,17 +12362,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>2591098</t>
+          <t>2569628</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>2591098</t>
+          <t>2569628</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>2591098</t>
+          <t>2569628</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
